--- a/data_extactor/batch_10_fa/trimmed/batch_0100_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0100_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب</t>
+          <t>گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | قدرت تنه | انعطاف‌پذیری بدنی | چابکی دستی | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | درک شفاهی | قدرت تنه | انعطاف‌پذیری دامنه حرکت | مهارت دستی | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | کارمندان ثبت و پردازش سفارش‌ها | کارگران بسته‌بندی دستی | کارمندان تدارکات و خرید | فروشندگان خرده‌فروشی | کارمندان انبارداری، تحویل، ارسال و کنترل موجودی کالا</t>
+          <t>صندوق‌داران | کارگران جابه‌جایی دستی بار، کالا و مصالح | متصدیان ثبت و پیگیری سفارش‌ها | کارگران بسته‌بندی دستی | کارمندان تدارکات و کارپردازی | فروشندگان خرده‌فروشی | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل‌کننده‌های منطقی قابل‌برنامه‌ریزی PLC | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | نرم‌افزار Microsoft Office | Microsoft Office | Microsoft Outlook | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | درک مطلب | شنیدن فعال | نگارش | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | حساسیت به مسئله | دید نزدیک | هماهنگی چندعضو | دقت کنترل | مرتب‌سازی اطلاعات</t>
+          <t>ثبات دست و بازو | مهارت دستی | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات صنایع شیمیایی | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و ابزار دقیق، به‌جز درهای اتوماتیک | اپراتورهای تأسیسات پالایش و فرآورش گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای پمپ‌های صنعتی، به‌جز پمپ‌های سرچاهی نفت و گاز</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>سیستم مانیتورینگ و کنترل سرپرستی و گردآوری داده SCADA | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | پایگاه‌های داده عملیاتی | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار سیستم مدیریت رایانه‌ای نگهداری و تعمیرات CMMS | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Office | Microsoft Outlook | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | سرعت ادراک | دقت کنترل | مرتب‌سازی اطلاعات | پایداری دست و بازو</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | دقت کنترل | ترتیب‌دهی اطلاعات | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات صنایع شیمیایی | اپراتورهای فرآیند و بهره‌برداری تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و ابزار دقیق، به‌جز درهای اتوماتیک | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای تأسیسات تصفیه آب و فاضلاب صنعتی و شهری</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | دقت کنترل | هماهنگی چندعضو | زمان واکنش | چابکی دستی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان دکل‌های حفاری نفت و گاز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات پالایش و فرآورش گاز | مهندسان نفت | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن | اپراتورهای حفاری دورانی دکل در صنایع نفت و گاز | اپراتورهای دکل‌های تعمیراتی و خدمات چاه در صنایع نفت و گاز</t>
+          <t>دکل‌بانان نفت و گاز | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مهندسان نفت | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | حفاران دورانی نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضو | پایداری دست و بازو | قدرت ایستا | چابکی دستی | زمان واکنش | قدرت تنه | دید نزدیک</t>
+          <t>هماهنگی چند عضو | ثبات دست و بازو | قدرت ایستا | مهارت دستی | زمان عکس‌العمل | قدرت تنه | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران شست‌وشو و تنظیف خودروها و تجهیزات | کارگران تخصصی جمع‌آوری و امحای پسماندهای خطرناک | رانندگان کامیون‌های سنگین و تریلی | کارگران نگهداری و تعمیرات راه‌ها و جاده‌ها | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | رانندگان وانت‌بار و کامیونت‌های سبک | کارگران بازیافت و تفکیک پسماند</t>
+          <t>شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران امحا و پاک‌سازی مواد خطرناک | رانندگان خودروهای سنگین و کشنده‌ها | کارگران راهداری و نگهداری جاده‌ها | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | کارگران بازیافت و تفکیک پسماند</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>سیستم کنترل توزیع‌شده DCS | سیستم مدیریت انبار WMS | نرم‌افزار CompuWeigh GMS | سیستم‌عامل Linux | Microsoft Excel | Microsoft Office | SAP</t>
+          <t>سیستم کنترل توزیع‌شده DCS | نرم‌افزار CompuWeigh GMS | سیستم‌عامل Linux | نرم‌افزار Microsoft Office | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>حمل و نقل | تولید و فرآوری | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چندعضو | دید دور | کنترل نرخ سرعت | چابکی دستی | حساسیت به مسئله | ادراک عمق</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | کنترل نرخ | مهارت دستی | حساسیت به مسئله | درک عمق</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان سیستم‌های نوار نقاله و کانوایر | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای تراکتورها و لیفتراک‌های صنعتی | کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | اپراتورهای پمپاژ نفت، بهره‌برداری پالایشگاه و متصدیان سنجش مخازن</t>
+          <t>اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
+          <t>حمل و نقل | مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چندعضو | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارگران ساده و متصدیان دستی جابه‌جایی بار، کالا و محموله‌ها | اپراتورهای تراکتورها و لیفتراک‌های صنعتی | متصدیان تغذیه و تخلیه ماشین‌آلات صنعتی | اپراتورها و متصدیان سیستم‌های نوار نقاله و کانوایر | اپراتورهای جرثقیل و تاورکرین | متصدیان چیدمان و آماده‌سازی سفارش | کارمندان انبارداری، تحویل، ارسال و کنترل موجودی کالا</t>
+          <t>کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | متصدیان چیدمان و آماده‌سازی سفارش | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | مخابرات | رایانه و الکترونیک | جغرافیا | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | مخابرات | رایانه و الکترونیک | جغرافیا | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری و غیرنظامی | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک‌ها و تکنسین‌های خدمات و تعمیرات هواپیما | مدیران مدیریت بحران و شرایط اضطراری | کارشناسان لجستیک و زنجیره تأمین</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | خلبانان تجاری | کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | مکانیک و تکنسین خدمات هواپیما | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان لجستیک و مدیریت زنجیره تأمین</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل‌ونقل | مدیریت و امور اداری | فیزیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | حمل و نقل | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید دور | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی دور | دقت کنترل</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات و تعمیرات هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های ماشین‌آلات صنعتی | ریگرها و متصدیان بستن و مهار بار و دکل | اپراتورهای جرثقیل و تاورکرین | کارشناسان عملیات فرودگاهی | مدیران ترابری، انبارداری و توزیع</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک‌های ماشین‌آلات صنعتی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اپراتورهای جرثقیل و تاورکرین | کارشناسان عملیات فرودگاهی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | جغرافیا | حمل‌ونقل | مکانیک | مدیریت و امور اداری | مخابرات | پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | جغرافیا | حمل و نقل | مکانیک | مدیریت و اداره | مخابرات | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید دور | جهت‌یابی فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی دور | جهت‌گیری فضایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>افسران گشت پلیس و کلانتری | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | نگهبانان و مأموران حراست | مدیران مدیریت بحران و شرایط اضطراری | کارشناسان لجستیک و زنجیره تأمین | کارشناسان آموزش و توسعه منابع انسانی | کارگران مواد منفجره، متخصصان جابه‌جایی مهمات و آتشبارها</t>
+          <t>ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول پلیس و کارآگاهان | نگهبانان و ماموران حراست | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مواد منفجره و آتش‌باری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
